--- a/sinim_2024_limpia.xlsx
+++ b/sinim_2024_limpia.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{6363D728-E38A-4C32-83F5-8DCEFA6CE3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C734D9FE-7C25-406A-B4F3-78D62DFA527D}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C734D9FE-7C25-406A-B4F3-78D62DFA527D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
